--- a/data/Data_V2.xlsx
+++ b/data/Data_V2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9f352ed9e5ec6ce/플랜잇_철강inputoutput연구/modeling/steel_iotable/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="11_A7E0BFB399222FA6BC82968DF7E23EA048CB1917" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2D5D32A-493E-4239-80F4-E714D5CAB1B5}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="11_A7E0BFB399222FA6BC82968DF7E23EA048CB1917" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34678DE6-6798-4E91-B85D-10F0D784EAFA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SHOCK" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="438">
   <si>
     <t>내역</t>
   </si>
@@ -94,9 +94,6 @@
     <t>수소 가격</t>
   </si>
   <si>
-    <t>저위발열량기준</t>
-  </si>
-  <si>
     <t>천원/GJ</t>
   </si>
   <si>
@@ -692,11 +689,11 @@
   </si>
   <si>
     <t>부문</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>석탄사용감소량(누적)</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>0.0861</t>
@@ -1085,11 +1082,11 @@
       </rPr>
       <t>고용유발계수</t>
     </r>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>수소_부가가치유발계수</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>0.0222</t>
@@ -1366,6 +1363,93 @@
   </si>
   <si>
     <t>0.1429</t>
+  </si>
+  <si>
+    <t>음식료품</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재생에너지전력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가격</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>천원/kWh</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLANiT</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저위발열량기준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, PLANiT</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">POSCO </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사업보고서</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>재생에너지기업재단</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1374,11 +1458,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;_-;_-@"/>
     <numFmt numFmtId="177" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@"/>
-    <numFmt numFmtId="178" formatCode="0.000_ "/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1423,27 +1507,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3C78D8"/>
-      <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF3C78D8"/>
-      <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Arial"/>
       <family val="3"/>
@@ -1484,8 +1547,36 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1508,18 +1599,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE1E1E2"/>
         <bgColor rgb="FFE1E1E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9F2D0"/>
-        <bgColor rgb="FFD9F2D0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF83CAEB"/>
-        <bgColor rgb="FF83CAEB"/>
       </patternFill>
     </fill>
   </fills>
@@ -1640,7 +1719,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1660,36 +1739,30 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -2025,84 +2098,84 @@
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="21">
+        <v>19</v>
+      </c>
+      <c r="G2" s="17">
         <v>0</v>
       </c>
-      <c r="H2" s="21">
+      <c r="H2" s="17">
         <v>-636028484.40622115</v>
       </c>
-      <c r="I2" s="21">
+      <c r="I2" s="17">
         <v>-1161255514.8874223</v>
       </c>
-      <c r="J2" s="21">
+      <c r="J2" s="17">
         <v>-1161255514.8874218</v>
       </c>
-      <c r="K2" s="21">
+      <c r="K2" s="17">
         <v>-1371346348.3328123</v>
       </c>
-      <c r="L2" s="21">
+      <c r="L2" s="17">
         <v>-3152149612.6058397</v>
       </c>
-      <c r="M2" s="21">
+      <c r="M2" s="17">
         <v>-3152149612.6058412</v>
       </c>
-      <c r="N2" s="21">
+      <c r="N2" s="17">
         <v>-3152149612.6058412</v>
       </c>
-      <c r="O2" s="21">
+      <c r="O2" s="17">
         <v>-4145573278.2804456</v>
       </c>
-      <c r="P2" s="21">
+      <c r="P2" s="17">
         <v>-4145573278.2804456</v>
       </c>
-      <c r="Q2" s="21">
+      <c r="Q2" s="17">
         <v>-5403129098.4650421</v>
       </c>
-      <c r="R2" s="21">
+      <c r="R2" s="17">
         <v>-6228563983.9188652</v>
       </c>
-      <c r="S2" s="21">
+      <c r="S2" s="17">
         <v>-6950163944.3933878</v>
       </c>
-      <c r="T2" s="21">
+      <c r="T2" s="17">
         <v>-6950163944.3933878</v>
       </c>
-      <c r="U2" s="21">
+      <c r="U2" s="17">
         <v>-6950163944.3933878</v>
       </c>
-      <c r="V2" s="21">
+      <c r="V2" s="17">
         <v>-7583661513.6934519</v>
       </c>
-      <c r="W2" s="21">
+      <c r="W2" s="17">
         <v>-7583661513.6934519</v>
       </c>
-      <c r="X2" s="21">
+      <c r="X2" s="17">
         <v>-8282886292.5491648</v>
       </c>
-      <c r="Y2" s="21">
+      <c r="Y2" s="17">
         <v>-8282886292.5491648</v>
       </c>
-      <c r="Z2" s="21">
+      <c r="Z2" s="17">
         <v>-8947849131.3262768</v>
       </c>
-      <c r="AA2" s="21">
+      <c r="AA2" s="17">
         <v>-8947849131.3262768</v>
       </c>
-      <c r="AB2" s="21">
+      <c r="AB2" s="17">
         <v>-9514046338.6238899</v>
       </c>
-      <c r="AC2" s="21">
+      <c r="AC2" s="17">
         <v>-9514046338.6238899</v>
       </c>
-      <c r="AD2" s="21">
+      <c r="AD2" s="17">
         <v>-9514046338.6238899</v>
       </c>
-      <c r="AE2" s="21">
+      <c r="AE2" s="17">
         <v>-9514046338.6238899</v>
       </c>
-      <c r="AF2" s="21">
+      <c r="AF2" s="17">
         <v>-9514046338.6238899</v>
       </c>
     </row>
@@ -2111,85 +2184,85 @@
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="H3" s="21">
-        <v>15194811707.521196</v>
-      </c>
-      <c r="I3" s="21">
-        <v>15944817707.521196</v>
-      </c>
-      <c r="J3" s="21">
-        <v>15944817707.521196</v>
-      </c>
-      <c r="K3" s="21">
-        <v>16244820107.521196</v>
-      </c>
-      <c r="L3" s="21">
-        <v>16244820107.521196</v>
-      </c>
-      <c r="M3" s="21">
-        <v>16244820107.521196</v>
-      </c>
-      <c r="N3" s="21">
-        <v>15345562313.516396</v>
-      </c>
-      <c r="O3" s="21">
-        <v>15345562313.516396</v>
-      </c>
-      <c r="P3" s="21">
-        <v>15345562313.516396</v>
-      </c>
-      <c r="Q3" s="21">
-        <v>15345562313.516396</v>
-      </c>
-      <c r="R3" s="21">
-        <v>15345562313.516396</v>
-      </c>
-      <c r="S3" s="21">
-        <v>15345562313.516396</v>
-      </c>
-      <c r="T3" s="21">
-        <v>15345562313.516396</v>
-      </c>
-      <c r="U3" s="21">
-        <v>15345562313.516396</v>
-      </c>
-      <c r="V3" s="21">
-        <v>15345562313.516396</v>
-      </c>
-      <c r="W3" s="21">
-        <v>15345562313.516396</v>
-      </c>
-      <c r="X3" s="21">
-        <v>15345562313.516396</v>
-      </c>
-      <c r="Y3" s="21">
-        <v>15345562313.516396</v>
-      </c>
-      <c r="Z3" s="21">
-        <v>15345562313.516396</v>
-      </c>
-      <c r="AA3" s="21">
-        <v>15345562313.516396</v>
-      </c>
-      <c r="AB3" s="21">
-        <v>15345562313.516396</v>
-      </c>
-      <c r="AC3" s="21">
-        <v>15345562313.516396</v>
-      </c>
-      <c r="AD3" s="21">
-        <v>15345562313.516396</v>
-      </c>
-      <c r="AE3" s="21">
-        <v>15345562313.516396</v>
-      </c>
-      <c r="AF3" s="21">
-        <v>15345562313.516396</v>
+        <v>19</v>
+      </c>
+      <c r="G3" s="17">
+        <v>13545909750.548668</v>
+      </c>
+      <c r="H3" s="17">
+        <v>14819212824.570616</v>
+      </c>
+      <c r="I3" s="17">
+        <v>16172706688.913439</v>
+      </c>
+      <c r="J3" s="17">
+        <v>16819614956.469976</v>
+      </c>
+      <c r="K3" s="17">
+        <v>17821519770.741165</v>
+      </c>
+      <c r="L3" s="17">
+        <v>18534380561.570812</v>
+      </c>
+      <c r="M3" s="17">
+        <v>19275755784.033646</v>
+      </c>
+      <c r="N3" s="17">
+        <v>18937064365.677006</v>
+      </c>
+      <c r="O3" s="17">
+        <v>19694546940.304085</v>
+      </c>
+      <c r="P3" s="17">
+        <v>20482328817.916248</v>
+      </c>
+      <c r="Q3" s="17">
+        <v>21301621970.6329</v>
+      </c>
+      <c r="R3" s="17">
+        <v>21301621970.6329</v>
+      </c>
+      <c r="S3" s="17">
+        <v>21301621970.6329</v>
+      </c>
+      <c r="T3" s="17">
+        <v>21301621970.6329</v>
+      </c>
+      <c r="U3" s="17">
+        <v>21301621970.6329</v>
+      </c>
+      <c r="V3" s="17">
+        <v>21301621970.6329</v>
+      </c>
+      <c r="W3" s="17">
+        <v>21301621970.6329</v>
+      </c>
+      <c r="X3" s="17">
+        <v>21301621970.6329</v>
+      </c>
+      <c r="Y3" s="17">
+        <v>21301621970.6329</v>
+      </c>
+      <c r="Z3" s="17">
+        <v>21301621970.6329</v>
+      </c>
+      <c r="AA3" s="17">
+        <v>21301621970.6329</v>
+      </c>
+      <c r="AB3" s="17">
+        <v>21301621970.6329</v>
+      </c>
+      <c r="AC3" s="17">
+        <v>21301621970.6329</v>
+      </c>
+      <c r="AD3" s="17">
+        <v>21301621970.6329</v>
+      </c>
+      <c r="AE3" s="17">
+        <v>21301621970.6329</v>
+      </c>
+      <c r="AF3" s="17">
+        <v>21301621970.6329</v>
       </c>
     </row>
     <row r="4" spans="1:34" ht="12.75">
@@ -2197,85 +2270,85 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="H4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="I4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="J4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="K4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="L4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="M4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="N4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="O4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="P4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="Q4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="R4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="S4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="T4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="U4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="V4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="W4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="X4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="Y4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="Z4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="AA4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="AB4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="AC4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="AD4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="AE4" s="21">
-        <v>14444805707.521196</v>
-      </c>
-      <c r="AF4" s="21">
-        <v>14444805707.521196</v>
+        <v>19</v>
+      </c>
+      <c r="G4" s="17">
+        <v>13545909750.548668</v>
+      </c>
+      <c r="H4" s="17">
+        <v>14087746140.570616</v>
+      </c>
+      <c r="I4" s="17">
+        <v>14651255986.193439</v>
+      </c>
+      <c r="J4" s="17">
+        <v>15237306225.641176</v>
+      </c>
+      <c r="K4" s="17">
+        <v>15846798474.666822</v>
+      </c>
+      <c r="L4" s="17">
+        <v>16480670413.653496</v>
+      </c>
+      <c r="M4" s="17">
+        <v>17139897230.199636</v>
+      </c>
+      <c r="N4" s="17">
+        <v>17825493119.407623</v>
+      </c>
+      <c r="O4" s="17">
+        <v>18538512844.183929</v>
+      </c>
+      <c r="P4" s="17">
+        <v>19280053357.951286</v>
+      </c>
+      <c r="Q4" s="17">
+        <v>20051255492.269341</v>
+      </c>
+      <c r="R4" s="17">
+        <v>20051255492.269341</v>
+      </c>
+      <c r="S4" s="17">
+        <v>20051255492.269341</v>
+      </c>
+      <c r="T4" s="17">
+        <v>20051255492.269341</v>
+      </c>
+      <c r="U4" s="17">
+        <v>20051255492.269341</v>
+      </c>
+      <c r="V4" s="17">
+        <v>20051255492.269341</v>
+      </c>
+      <c r="W4" s="17">
+        <v>20051255492.269341</v>
+      </c>
+      <c r="X4" s="17">
+        <v>20051255492.269341</v>
+      </c>
+      <c r="Y4" s="17">
+        <v>20051255492.269341</v>
+      </c>
+      <c r="Z4" s="17">
+        <v>20051255492.269341</v>
+      </c>
+      <c r="AA4" s="17">
+        <v>20051255492.269341</v>
+      </c>
+      <c r="AB4" s="17">
+        <v>20051255492.269341</v>
+      </c>
+      <c r="AC4" s="17">
+        <v>20051255492.269341</v>
+      </c>
+      <c r="AD4" s="17">
+        <v>20051255492.269341</v>
+      </c>
+      <c r="AE4" s="17">
+        <v>20051255492.269341</v>
+      </c>
+      <c r="AF4" s="17">
+        <v>20051255492.269341</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="12.75">
@@ -2283,85 +2356,85 @@
         <v>10</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="21">
+        <v>19</v>
+      </c>
+      <c r="G5" s="17">
         <v>0</v>
       </c>
-      <c r="H5" s="21">
-        <v>750005999.99999988</v>
-      </c>
-      <c r="I5" s="21">
-        <v>1500011999.9999998</v>
-      </c>
-      <c r="J5" s="21">
-        <v>1500011999.9999998</v>
-      </c>
-      <c r="K5" s="21">
-        <v>1800014399.9999995</v>
-      </c>
-      <c r="L5" s="21">
-        <v>1800014399.9999995</v>
-      </c>
-      <c r="M5" s="21">
-        <v>1800014399.9999995</v>
-      </c>
-      <c r="N5" s="21">
-        <v>900756605.9951998</v>
-      </c>
-      <c r="O5" s="21">
-        <v>900756605.9951998</v>
-      </c>
-      <c r="P5" s="21">
-        <v>900756605.9951998</v>
-      </c>
-      <c r="Q5" s="21">
-        <v>900756605.9951998</v>
-      </c>
-      <c r="R5" s="21">
-        <v>900756605.9951998</v>
-      </c>
-      <c r="S5" s="21">
-        <v>900756605.9951998</v>
-      </c>
-      <c r="T5" s="21">
-        <v>900756605.9951998</v>
-      </c>
-      <c r="U5" s="21">
-        <v>900756605.9951998</v>
-      </c>
-      <c r="V5" s="21">
-        <v>900756605.9951998</v>
-      </c>
-      <c r="W5" s="21">
-        <v>900756605.9951998</v>
-      </c>
-      <c r="X5" s="21">
-        <v>900756605.9951998</v>
-      </c>
-      <c r="Y5" s="21">
-        <v>900756605.9951998</v>
-      </c>
-      <c r="Z5" s="21">
-        <v>900756605.9951998</v>
-      </c>
-      <c r="AA5" s="21">
-        <v>900756605.9951998</v>
-      </c>
-      <c r="AB5" s="21">
-        <v>900756605.9951998</v>
-      </c>
-      <c r="AC5" s="21">
-        <v>900756605.9951998</v>
-      </c>
-      <c r="AD5" s="21">
-        <v>900756605.9951998</v>
-      </c>
-      <c r="AE5" s="21">
-        <v>900756605.9951998</v>
-      </c>
-      <c r="AF5" s="21">
-        <v>900756605.9951998</v>
+      <c r="H5" s="17">
+        <v>731466684</v>
+      </c>
+      <c r="I5" s="17">
+        <v>1521450702.72</v>
+      </c>
+      <c r="J5" s="17">
+        <v>1582308730.8288</v>
+      </c>
+      <c r="K5" s="17">
+        <v>1974721296.074342</v>
+      </c>
+      <c r="L5" s="17">
+        <v>2053710147.9173157</v>
+      </c>
+      <c r="M5" s="17">
+        <v>2135858553.8340085</v>
+      </c>
+      <c r="N5" s="17">
+        <v>1111571246.2693808</v>
+      </c>
+      <c r="O5" s="17">
+        <v>1156034096.120156</v>
+      </c>
+      <c r="P5" s="17">
+        <v>1202275459.964962</v>
+      </c>
+      <c r="Q5" s="17">
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="R5" s="17">
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="S5" s="17">
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="T5" s="17">
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="U5" s="17">
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="V5" s="17">
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="W5" s="17">
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="X5" s="17">
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="Y5" s="17">
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="Z5" s="17">
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="AA5" s="17">
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="AB5" s="17">
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="AC5" s="17">
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="AD5" s="17">
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="AE5" s="17">
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="AF5" s="17">
+        <v>1250366478.3635607</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="12.75">
@@ -2369,96 +2442,96 @@
         <v>11</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="21">
+        <v>19</v>
+      </c>
+      <c r="G6" s="17">
         <v>0</v>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="17">
         <v>0</v>
       </c>
-      <c r="I6" s="21">
+      <c r="I6" s="17">
         <v>0</v>
       </c>
-      <c r="J6" s="21">
+      <c r="J6" s="17">
         <v>0</v>
       </c>
-      <c r="K6" s="21">
+      <c r="K6" s="17">
         <v>0</v>
       </c>
-      <c r="L6" s="21">
-        <v>2495899463.9590001</v>
-      </c>
-      <c r="M6" s="21">
-        <v>2495899463.9590001</v>
-      </c>
-      <c r="N6" s="21">
-        <v>3493819887.5889997</v>
-      </c>
-      <c r="O6" s="21">
-        <v>5849955000</v>
-      </c>
-      <c r="P6" s="21">
-        <v>5849955000</v>
-      </c>
-      <c r="Q6" s="21">
-        <v>8883265000</v>
-      </c>
-      <c r="R6" s="21">
-        <v>10833250000</v>
-      </c>
-      <c r="S6" s="21">
-        <v>12566570000</v>
-      </c>
-      <c r="T6" s="21">
-        <v>12566570000</v>
-      </c>
-      <c r="U6" s="21">
-        <v>12566570000</v>
-      </c>
-      <c r="V6" s="21">
-        <v>14083225000</v>
-      </c>
-      <c r="W6" s="21">
-        <v>14083225000</v>
-      </c>
-      <c r="X6" s="21">
-        <v>15773212000</v>
-      </c>
-      <c r="Y6" s="21">
-        <v>15773212000</v>
-      </c>
-      <c r="Z6" s="21">
-        <v>17333200000</v>
-      </c>
-      <c r="AA6" s="21">
-        <v>17333200000</v>
-      </c>
-      <c r="AB6" s="21">
-        <v>18676523000</v>
-      </c>
-      <c r="AC6" s="21">
-        <v>18676523000</v>
-      </c>
-      <c r="AD6" s="21">
-        <v>18676523000</v>
-      </c>
-      <c r="AE6" s="21">
-        <v>18676523000</v>
-      </c>
-      <c r="AF6" s="21">
-        <v>18676523000</v>
+      <c r="L6" s="17">
+        <v>4976477827.2000008</v>
+      </c>
+      <c r="M6" s="17">
+        <v>4792643625.9645901</v>
+      </c>
+      <c r="N6" s="17">
+        <v>6513336370.4258909</v>
+      </c>
+      <c r="O6" s="17">
+        <v>10652624550</v>
+      </c>
+      <c r="P6" s="17">
+        <v>10588499550</v>
+      </c>
+      <c r="Q6" s="17">
+        <v>15875542350</v>
+      </c>
+      <c r="R6" s="17">
+        <v>19097917500</v>
+      </c>
+      <c r="S6" s="17">
+        <v>20744665700</v>
+      </c>
+      <c r="T6" s="17">
+        <v>19848084300</v>
+      </c>
+      <c r="U6" s="17">
+        <v>18992584300</v>
+      </c>
+      <c r="V6" s="17">
+        <v>20372082250</v>
+      </c>
+      <c r="W6" s="17">
+        <v>19500000000</v>
+      </c>
+      <c r="X6" s="17">
+        <v>20908767880</v>
+      </c>
+      <c r="Y6" s="17">
+        <v>20020000000</v>
+      </c>
+      <c r="Z6" s="17">
+        <v>21066668000</v>
+      </c>
+      <c r="AA6" s="17">
+        <v>20176667999.999996</v>
+      </c>
+      <c r="AB6" s="17">
+        <v>20824484769.999996</v>
+      </c>
+      <c r="AC6" s="17">
+        <v>19944525000</v>
+      </c>
+      <c r="AD6" s="17">
+        <v>19104075000</v>
+      </c>
+      <c r="AE6" s="17">
+        <v>18299540230</v>
+      </c>
+      <c r="AF6" s="17">
+        <v>17530925000</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BD16733-54D7-4FF2-ADA4-F0713D0B7C4B}">
-  <dimension ref="A1:AH17"/>
+  <dimension ref="A1:AH24"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.42578125" customWidth="1"/>
@@ -2652,8 +2725,8 @@
       </c>
     </row>
     <row r="3" spans="1:34" ht="13.5">
-      <c r="A3" s="22" t="s">
-        <v>218</v>
+      <c r="A3" s="18" t="s">
+        <v>217</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>4</v>
@@ -3138,839 +3211,990 @@
         <v>431000000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" ht="15">
-      <c r="A9" s="2" t="s">
+    <row r="11" spans="1:34" ht="15">
+      <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="B11" s="29" t="s">
+        <v>436</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D11" s="4">
         <v>472</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E11" s="5">
         <v>387</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F11" s="5">
         <v>329</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G11" s="2">
         <v>396</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H11" s="2">
         <v>396</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I11" s="2">
         <v>396</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J11" s="2">
         <v>396</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K11" s="2">
         <v>396</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L11" s="2">
         <v>396</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M11" s="2">
         <v>396</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N11" s="2">
         <v>396</v>
       </c>
-      <c r="O9" s="2">
+      <c r="O11" s="2">
         <v>396</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P11" s="2">
         <v>396</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q11" s="2">
         <v>396</v>
       </c>
-      <c r="R9" s="2">
+      <c r="R11" s="2">
         <v>396</v>
       </c>
-      <c r="S9" s="2">
+      <c r="S11" s="2">
         <v>396</v>
       </c>
-      <c r="T9" s="2">
+      <c r="T11" s="2">
         <v>396</v>
       </c>
-      <c r="U9" s="2">
+      <c r="U11" s="2">
         <v>396</v>
       </c>
-      <c r="V9" s="2">
+      <c r="V11" s="2">
         <v>396</v>
       </c>
-      <c r="W9" s="2">
+      <c r="W11" s="2">
         <v>396</v>
       </c>
-      <c r="X9" s="2">
+      <c r="X11" s="2">
         <v>396</v>
       </c>
-      <c r="Y9" s="2">
+      <c r="Y11" s="2">
         <v>396</v>
       </c>
-      <c r="Z9" s="2">
+      <c r="Z11" s="2">
         <v>396</v>
       </c>
-      <c r="AA9" s="2">
+      <c r="AA11" s="2">
         <v>396</v>
       </c>
-      <c r="AB9" s="2">
+      <c r="AB11" s="2">
         <v>396</v>
       </c>
-      <c r="AC9" s="2">
+      <c r="AC11" s="2">
         <v>396</v>
       </c>
-      <c r="AD9" s="2">
+      <c r="AD11" s="2">
         <v>396</v>
       </c>
-      <c r="AE9" s="2">
+      <c r="AE11" s="2">
         <v>396</v>
       </c>
-      <c r="AF9" s="2">
+      <c r="AF11" s="2">
         <v>396</v>
       </c>
     </row>
-    <row r="10" spans="1:34" ht="12.75">
-      <c r="A10" s="2" t="s">
+    <row r="12" spans="1:34" ht="13.5">
+      <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="B12" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G12" s="2">
         <v>0.18</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H12" s="2">
         <v>0.18</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I12" s="2">
         <v>0.18</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J12" s="2">
         <v>0.18</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K12" s="2">
         <v>0.18</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L12" s="2">
         <v>0.18</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M12" s="2">
         <v>0.18</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N12" s="2">
         <v>0.18</v>
       </c>
-      <c r="O10" s="2">
+      <c r="O12" s="2">
         <v>0.18</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P12" s="2">
         <v>0.18</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q12" s="2">
         <v>0.18</v>
       </c>
-      <c r="R10" s="2">
+      <c r="R12" s="2">
         <v>0.18</v>
       </c>
-      <c r="S10" s="2">
+      <c r="S12" s="2">
         <v>0.18</v>
       </c>
-      <c r="T10" s="2">
+      <c r="T12" s="2">
         <v>0.18</v>
       </c>
-      <c r="U10" s="2">
+      <c r="U12" s="2">
         <v>0.18</v>
       </c>
-      <c r="V10" s="2">
+      <c r="V12" s="2">
         <v>0.18</v>
       </c>
-      <c r="W10" s="2">
+      <c r="W12" s="2">
         <v>0.18</v>
       </c>
-      <c r="X10" s="2">
+      <c r="X12" s="2">
         <v>0.18</v>
       </c>
-      <c r="Y10" s="2">
+      <c r="Y12" s="2">
         <v>0.18</v>
       </c>
-      <c r="Z10" s="2">
+      <c r="Z12" s="2">
         <v>0.18</v>
       </c>
-      <c r="AA10" s="2">
+      <c r="AA12" s="2">
         <v>0.18</v>
       </c>
-      <c r="AB10" s="2">
+      <c r="AB12" s="2">
         <v>0.18</v>
       </c>
-      <c r="AC10" s="2">
+      <c r="AC12" s="2">
         <v>0.18</v>
       </c>
-      <c r="AD10" s="2">
+      <c r="AD12" s="2">
         <v>0.18</v>
       </c>
-      <c r="AE10" s="2">
+      <c r="AE12" s="2">
         <v>0.18</v>
       </c>
-      <c r="AF10" s="2">
+      <c r="AF12" s="2">
         <v>0.18</v>
       </c>
     </row>
-    <row r="11" spans="1:34" ht="12.75">
-      <c r="A11" s="2" t="s">
+    <row r="13" spans="1:34" ht="13.5">
+      <c r="A13" s="28" t="s">
+        <v>432</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>434</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>433</v>
+      </c>
+      <c r="G13" s="27">
+        <v>0.16879865361077112</v>
+      </c>
+      <c r="H13" s="27">
+        <v>0.17555059975520199</v>
+      </c>
+      <c r="I13" s="27">
+        <v>0.18257262374541006</v>
+      </c>
+      <c r="J13" s="27">
+        <v>0.18987552869522645</v>
+      </c>
+      <c r="K13" s="27">
+        <v>0.1974705498430355</v>
+      </c>
+      <c r="L13" s="27">
+        <v>0.20536937183675691</v>
+      </c>
+      <c r="M13" s="27">
+        <v>0.21358414671022721</v>
+      </c>
+      <c r="N13" s="27">
+        <v>0.22212751257863633</v>
+      </c>
+      <c r="O13" s="27">
+        <v>0.23101261308178178</v>
+      </c>
+      <c r="P13" s="27">
+        <v>0.24025311760505302</v>
+      </c>
+      <c r="Q13" s="27">
+        <v>0.24986324230925519</v>
+      </c>
+      <c r="R13" s="27">
+        <v>0.24986324230925519</v>
+      </c>
+      <c r="S13" s="27">
+        <v>0.24986324230925519</v>
+      </c>
+      <c r="T13" s="27">
+        <v>0.24986324230925519</v>
+      </c>
+      <c r="U13" s="27">
+        <v>0.24986324230925519</v>
+      </c>
+      <c r="V13" s="27">
+        <v>0.24986324230925519</v>
+      </c>
+      <c r="W13" s="27">
+        <v>0.24986324230925519</v>
+      </c>
+      <c r="X13" s="27">
+        <v>0.24986324230925519</v>
+      </c>
+      <c r="Y13" s="27">
+        <v>0.24986324230925519</v>
+      </c>
+      <c r="Z13" s="27">
+        <v>0.24986324230925519</v>
+      </c>
+      <c r="AA13" s="27">
+        <v>0.24986324230925519</v>
+      </c>
+      <c r="AB13" s="27">
+        <v>0.24986324230925519</v>
+      </c>
+      <c r="AC13" s="27">
+        <v>0.24986324230925519</v>
+      </c>
+      <c r="AD13" s="27">
+        <v>0.24986324230925519</v>
+      </c>
+      <c r="AE13" s="27">
+        <v>0.24986324230925519</v>
+      </c>
+      <c r="AF13" s="27">
+        <v>0.24986324230925519</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" ht="13.5">
+      <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B14" s="30" t="s">
+        <v>435</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="G14" s="27">
+        <v>90.716669999999993</v>
+      </c>
+      <c r="H14" s="27">
+        <v>89.674999999999997</v>
+      </c>
+      <c r="I14" s="27">
+        <v>87.974999999999994</v>
+      </c>
+      <c r="J14" s="27">
+        <v>89.741669999999999</v>
+      </c>
+      <c r="K14" s="27">
+        <v>89.8</v>
+      </c>
+      <c r="L14" s="27">
+        <v>86.4</v>
+      </c>
+      <c r="M14" s="27">
+        <v>83.208330000000004</v>
+      </c>
+      <c r="N14" s="27">
+        <v>80.783330000000007</v>
+      </c>
+      <c r="O14" s="27">
+        <v>78.908330000000007</v>
+      </c>
+      <c r="P14" s="27">
+        <v>78.433329999999998</v>
+      </c>
+      <c r="Q14" s="27">
+        <v>77.441670000000002</v>
+      </c>
+      <c r="R14" s="27">
+        <v>76.391670000000005</v>
+      </c>
+      <c r="S14" s="27">
+        <v>71.533330000000007</v>
+      </c>
+      <c r="T14" s="27">
+        <v>68.441670000000002</v>
+      </c>
+      <c r="U14" s="27">
+        <v>65.491669999999999</v>
+      </c>
+      <c r="V14" s="27">
+        <v>62.683330000000005</v>
+      </c>
+      <c r="W14" s="27">
+        <v>60</v>
+      </c>
+      <c r="X14" s="27">
+        <v>57.441669999999995</v>
+      </c>
+      <c r="Y14" s="27">
+        <v>55</v>
+      </c>
+      <c r="Z14" s="27">
+        <v>52.666669999999996</v>
+      </c>
+      <c r="AA14" s="27">
+        <v>50.441669999999995</v>
+      </c>
+      <c r="AB14" s="27">
+        <v>48.316669999999995</v>
+      </c>
+      <c r="AC14" s="27">
+        <v>46.274999999999999</v>
+      </c>
+      <c r="AD14" s="27">
+        <v>44.325000000000003</v>
+      </c>
+      <c r="AE14" s="27">
+        <v>42.458330000000004</v>
+      </c>
+      <c r="AF14" s="27">
+        <v>40.674999999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" ht="16.5" customHeight="1"/>
+    <row r="16" spans="1:34" ht="12.75">
+      <c r="A16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="H11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="I11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="J11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="K11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="L11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="M11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="N11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="O11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="P11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="R11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="S11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="T11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="U11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="V11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="W11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="X11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="Y11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="Z11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="AA11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="AB11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="AC11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="AD11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="AE11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-      <c r="AF11" s="2">
-        <v>43.332999999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:34" ht="16.5" customHeight="1"/>
-    <row r="13" spans="1:34" ht="12.75">
-      <c r="A13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13" s="20">
-        <f>G3*1000*G9</f>
+      <c r="G16" s="16">
+        <f>G3*1000*G11</f>
         <v>0</v>
       </c>
-      <c r="H13" s="20">
-        <f t="shared" ref="H13:AF13" si="2">H3*1000*H9</f>
+      <c r="H16" s="16">
+        <f>H3*1000*H11</f>
         <v>-636028484.40622115</v>
       </c>
-      <c r="I13" s="20">
-        <f t="shared" si="2"/>
+      <c r="I16" s="16">
+        <f>I3*1000*I11</f>
         <v>-1161255514.8874223</v>
       </c>
-      <c r="J13" s="20">
-        <f t="shared" si="2"/>
+      <c r="J16" s="16">
+        <f>J3*1000*J11</f>
         <v>-1161255514.8874218</v>
       </c>
-      <c r="K13" s="20">
-        <f t="shared" si="2"/>
+      <c r="K16" s="16">
+        <f>K3*1000*K11</f>
         <v>-1371346348.3328123</v>
       </c>
-      <c r="L13" s="20">
-        <f t="shared" si="2"/>
+      <c r="L16" s="16">
+        <f>L3*1000*L11</f>
         <v>-3152149612.6058397</v>
       </c>
-      <c r="M13" s="20">
-        <f t="shared" si="2"/>
+      <c r="M16" s="16">
+        <f>M3*1000*M11</f>
         <v>-3152149612.6058412</v>
       </c>
-      <c r="N13" s="20">
-        <f t="shared" si="2"/>
+      <c r="N16" s="16">
+        <f>N3*1000*N11</f>
         <v>-3152149612.6058412</v>
       </c>
-      <c r="O13" s="20">
-        <f t="shared" si="2"/>
+      <c r="O16" s="16">
+        <f>O3*1000*O11</f>
         <v>-4145573278.2804456</v>
       </c>
-      <c r="P13" s="20">
-        <f t="shared" si="2"/>
+      <c r="P16" s="16">
+        <f>P3*1000*P11</f>
         <v>-4145573278.2804456</v>
       </c>
-      <c r="Q13" s="20">
-        <f t="shared" si="2"/>
+      <c r="Q16" s="16">
+        <f>Q3*1000*Q11</f>
         <v>-5403129098.4650421</v>
       </c>
-      <c r="R13" s="20">
-        <f t="shared" si="2"/>
+      <c r="R16" s="16">
+        <f>R3*1000*R11</f>
         <v>-6228563983.9188652</v>
       </c>
-      <c r="S13" s="20">
-        <f t="shared" si="2"/>
+      <c r="S16" s="16">
+        <f>S3*1000*S11</f>
         <v>-6950163944.3933878</v>
       </c>
-      <c r="T13" s="20">
-        <f t="shared" si="2"/>
+      <c r="T16" s="16">
+        <f>T3*1000*T11</f>
         <v>-6950163944.3933878</v>
       </c>
-      <c r="U13" s="20">
-        <f t="shared" si="2"/>
+      <c r="U16" s="16">
+        <f>U3*1000*U11</f>
         <v>-6950163944.3933878</v>
       </c>
-      <c r="V13" s="20">
-        <f t="shared" si="2"/>
+      <c r="V16" s="16">
+        <f>V3*1000*V11</f>
         <v>-7583661513.6934519</v>
       </c>
-      <c r="W13" s="20">
-        <f t="shared" si="2"/>
+      <c r="W16" s="16">
+        <f>W3*1000*W11</f>
         <v>-7583661513.6934519</v>
       </c>
-      <c r="X13" s="20">
-        <f t="shared" si="2"/>
+      <c r="X16" s="16">
+        <f>X3*1000*X11</f>
         <v>-8282886292.5491648</v>
       </c>
-      <c r="Y13" s="20">
-        <f t="shared" si="2"/>
+      <c r="Y16" s="16">
+        <f>Y3*1000*Y11</f>
         <v>-8282886292.5491648</v>
       </c>
-      <c r="Z13" s="20">
-        <f t="shared" si="2"/>
+      <c r="Z16" s="16">
+        <f>Z3*1000*Z11</f>
         <v>-8947849131.3262768</v>
       </c>
-      <c r="AA13" s="20">
-        <f t="shared" si="2"/>
+      <c r="AA16" s="16">
+        <f t="shared" ref="AA16:AF16" si="2">AA3*1000*AA11</f>
         <v>-8947849131.3262768</v>
       </c>
-      <c r="AB13" s="20">
+      <c r="AB16" s="16">
         <f t="shared" si="2"/>
         <v>-9514046338.6238899</v>
       </c>
-      <c r="AC13" s="20">
+      <c r="AC16" s="16">
         <f t="shared" si="2"/>
         <v>-9514046338.6238899</v>
       </c>
-      <c r="AD13" s="20">
+      <c r="AD16" s="16">
         <f t="shared" si="2"/>
         <v>-9514046338.6238899</v>
       </c>
-      <c r="AE13" s="20">
+      <c r="AE16" s="16">
         <f t="shared" si="2"/>
         <v>-9514046338.6238899</v>
       </c>
-      <c r="AF13" s="20">
+      <c r="AF16" s="16">
         <f t="shared" si="2"/>
         <v>-9514046338.6238899</v>
       </c>
     </row>
-    <row r="14" spans="1:34" ht="12.75">
-      <c r="A14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="20">
-        <f t="shared" ref="G14:AF14" si="3">G4*G10</f>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="H14" s="20">
-        <f t="shared" si="3"/>
-        <v>15194811707.521196</v>
-      </c>
-      <c r="I14" s="20">
-        <f t="shared" si="3"/>
-        <v>15944817707.521196</v>
-      </c>
-      <c r="J14" s="20">
-        <f t="shared" si="3"/>
-        <v>15944817707.521196</v>
-      </c>
-      <c r="K14" s="20">
-        <f t="shared" si="3"/>
-        <v>16244820107.521196</v>
-      </c>
-      <c r="L14" s="20">
-        <f t="shared" si="3"/>
-        <v>16244820107.521196</v>
-      </c>
-      <c r="M14" s="20">
-        <f t="shared" si="3"/>
-        <v>16244820107.521196</v>
-      </c>
-      <c r="N14" s="20">
-        <f t="shared" si="3"/>
-        <v>15345562313.516396</v>
-      </c>
-      <c r="O14" s="20">
-        <f t="shared" si="3"/>
-        <v>15345562313.516396</v>
-      </c>
-      <c r="P14" s="20">
-        <f t="shared" si="3"/>
-        <v>15345562313.516396</v>
-      </c>
-      <c r="Q14" s="20">
-        <f t="shared" si="3"/>
-        <v>15345562313.516396</v>
-      </c>
-      <c r="R14" s="20">
-        <f t="shared" si="3"/>
-        <v>15345562313.516396</v>
-      </c>
-      <c r="S14" s="20">
-        <f t="shared" si="3"/>
-        <v>15345562313.516396</v>
-      </c>
-      <c r="T14" s="20">
-        <f t="shared" si="3"/>
-        <v>15345562313.516396</v>
-      </c>
-      <c r="U14" s="20">
-        <f t="shared" si="3"/>
-        <v>15345562313.516396</v>
-      </c>
-      <c r="V14" s="20">
-        <f t="shared" si="3"/>
-        <v>15345562313.516396</v>
-      </c>
-      <c r="W14" s="20">
-        <f t="shared" si="3"/>
-        <v>15345562313.516396</v>
-      </c>
-      <c r="X14" s="20">
-        <f t="shared" si="3"/>
-        <v>15345562313.516396</v>
-      </c>
-      <c r="Y14" s="20">
-        <f t="shared" si="3"/>
-        <v>15345562313.516396</v>
-      </c>
-      <c r="Z14" s="20">
-        <f t="shared" si="3"/>
-        <v>15345562313.516396</v>
-      </c>
-      <c r="AA14" s="20">
-        <f t="shared" si="3"/>
-        <v>15345562313.516396</v>
-      </c>
-      <c r="AB14" s="20">
-        <f t="shared" si="3"/>
-        <v>15345562313.516396</v>
-      </c>
-      <c r="AC14" s="20">
-        <f t="shared" si="3"/>
-        <v>15345562313.516396</v>
-      </c>
-      <c r="AD14" s="20">
-        <f t="shared" si="3"/>
-        <v>15345562313.516396</v>
-      </c>
-      <c r="AE14" s="20">
-        <f t="shared" si="3"/>
-        <v>15345562313.516396</v>
-      </c>
-      <c r="AF14" s="20">
-        <f t="shared" si="3"/>
-        <v>15345562313.516396</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" ht="12.75">
-      <c r="A15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="20">
-        <f t="shared" ref="G15:AF15" si="4">G5*G10</f>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="H15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="I15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="J15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="K15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="L15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="M15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="N15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="O15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="P15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="Q15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="R15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="S15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="T15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="U15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="V15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="W15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="X15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="Y15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="Z15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="AA15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="AB15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="AC15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="AD15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="AE15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-      <c r="AF15" s="20">
-        <f t="shared" si="4"/>
-        <v>14444805707.521196</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" ht="12.75">
-      <c r="A16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G16" s="20">
-        <f t="shared" ref="G16:AF17" si="5">G6*G10</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="20">
-        <f t="shared" si="5"/>
-        <v>750005999.99999988</v>
-      </c>
-      <c r="I16" s="20">
-        <f t="shared" si="5"/>
-        <v>1500011999.9999998</v>
-      </c>
-      <c r="J16" s="20">
-        <f t="shared" si="5"/>
-        <v>1500011999.9999998</v>
-      </c>
-      <c r="K16" s="20">
-        <f t="shared" si="5"/>
-        <v>1800014399.9999995</v>
-      </c>
-      <c r="L16" s="20">
-        <f t="shared" si="5"/>
-        <v>1800014399.9999995</v>
-      </c>
-      <c r="M16" s="20">
-        <f t="shared" si="5"/>
-        <v>1800014399.9999995</v>
-      </c>
-      <c r="N16" s="20">
-        <f t="shared" si="5"/>
-        <v>900756605.9951998</v>
-      </c>
-      <c r="O16" s="20">
-        <f t="shared" si="5"/>
-        <v>900756605.9951998</v>
-      </c>
-      <c r="P16" s="20">
-        <f t="shared" si="5"/>
-        <v>900756605.9951998</v>
-      </c>
-      <c r="Q16" s="20">
-        <f t="shared" si="5"/>
-        <v>900756605.9951998</v>
-      </c>
-      <c r="R16" s="20">
-        <f t="shared" si="5"/>
-        <v>900756605.9951998</v>
-      </c>
-      <c r="S16" s="20">
-        <f t="shared" si="5"/>
-        <v>900756605.9951998</v>
-      </c>
-      <c r="T16" s="20">
-        <f t="shared" si="5"/>
-        <v>900756605.9951998</v>
-      </c>
-      <c r="U16" s="20">
-        <f t="shared" si="5"/>
-        <v>900756605.9951998</v>
-      </c>
-      <c r="V16" s="20">
-        <f t="shared" si="5"/>
-        <v>900756605.9951998</v>
-      </c>
-      <c r="W16" s="20">
-        <f t="shared" si="5"/>
-        <v>900756605.9951998</v>
-      </c>
-      <c r="X16" s="20">
-        <f t="shared" si="5"/>
-        <v>900756605.9951998</v>
-      </c>
-      <c r="Y16" s="20">
-        <f t="shared" si="5"/>
-        <v>900756605.9951998</v>
-      </c>
-      <c r="Z16" s="20">
-        <f t="shared" si="5"/>
-        <v>900756605.9951998</v>
-      </c>
-      <c r="AA16" s="20">
-        <f t="shared" si="5"/>
-        <v>900756605.9951998</v>
-      </c>
-      <c r="AB16" s="20">
-        <f t="shared" si="5"/>
-        <v>900756605.9951998</v>
-      </c>
-      <c r="AC16" s="20">
-        <f t="shared" si="5"/>
-        <v>900756605.9951998</v>
-      </c>
-      <c r="AD16" s="20">
-        <f t="shared" si="5"/>
-        <v>900756605.9951998</v>
-      </c>
-      <c r="AE16" s="20">
-        <f t="shared" si="5"/>
-        <v>900756605.9951998</v>
-      </c>
-      <c r="AF16" s="20">
-        <f t="shared" si="5"/>
-        <v>900756605.9951998</v>
-      </c>
-    </row>
     <row r="17" spans="1:32" ht="12.75">
       <c r="A17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="16">
+        <f>SUM(G18:G19)</f>
+        <v>13545909750.548668</v>
+      </c>
+      <c r="H17" s="16">
+        <f t="shared" ref="H17:AF17" si="3">SUM(H18:H19)</f>
+        <v>14819212824.570616</v>
+      </c>
+      <c r="I17" s="16">
+        <f t="shared" si="3"/>
+        <v>16172706688.913439</v>
+      </c>
+      <c r="J17" s="16">
+        <f t="shared" si="3"/>
+        <v>16819614956.469976</v>
+      </c>
+      <c r="K17" s="16">
+        <f t="shared" si="3"/>
+        <v>17821519770.741165</v>
+      </c>
+      <c r="L17" s="16">
+        <f t="shared" si="3"/>
+        <v>18534380561.570812</v>
+      </c>
+      <c r="M17" s="16">
+        <f t="shared" si="3"/>
+        <v>19275755784.033646</v>
+      </c>
+      <c r="N17" s="16">
+        <f t="shared" si="3"/>
+        <v>18937064365.677006</v>
+      </c>
+      <c r="O17" s="16">
+        <f t="shared" si="3"/>
+        <v>19694546940.304085</v>
+      </c>
+      <c r="P17" s="16">
+        <f t="shared" si="3"/>
+        <v>20482328817.916248</v>
+      </c>
+      <c r="Q17" s="16">
+        <f t="shared" si="3"/>
+        <v>21301621970.6329</v>
+      </c>
+      <c r="R17" s="16">
+        <f t="shared" si="3"/>
+        <v>21301621970.6329</v>
+      </c>
+      <c r="S17" s="16">
+        <f t="shared" si="3"/>
+        <v>21301621970.6329</v>
+      </c>
+      <c r="T17" s="16">
+        <f t="shared" si="3"/>
+        <v>21301621970.6329</v>
+      </c>
+      <c r="U17" s="16">
+        <f t="shared" si="3"/>
+        <v>21301621970.6329</v>
+      </c>
+      <c r="V17" s="16">
+        <f t="shared" si="3"/>
+        <v>21301621970.6329</v>
+      </c>
+      <c r="W17" s="16">
+        <f t="shared" si="3"/>
+        <v>21301621970.6329</v>
+      </c>
+      <c r="X17" s="16">
+        <f t="shared" si="3"/>
+        <v>21301621970.6329</v>
+      </c>
+      <c r="Y17" s="16">
+        <f t="shared" si="3"/>
+        <v>21301621970.6329</v>
+      </c>
+      <c r="Z17" s="16">
+        <f t="shared" si="3"/>
+        <v>21301621970.6329</v>
+      </c>
+      <c r="AA17" s="16">
+        <f t="shared" si="3"/>
+        <v>21301621970.6329</v>
+      </c>
+      <c r="AB17" s="16">
+        <f t="shared" si="3"/>
+        <v>21301621970.6329</v>
+      </c>
+      <c r="AC17" s="16">
+        <f t="shared" si="3"/>
+        <v>21301621970.6329</v>
+      </c>
+      <c r="AD17" s="16">
+        <f t="shared" si="3"/>
+        <v>21301621970.6329</v>
+      </c>
+      <c r="AE17" s="16">
+        <f t="shared" si="3"/>
+        <v>21301621970.6329</v>
+      </c>
+      <c r="AF17" s="16">
+        <f t="shared" si="3"/>
+        <v>21301621970.6329</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" ht="12.75">
+      <c r="A18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="16">
+        <f>G5*G13</f>
+        <v>13545909750.548668</v>
+      </c>
+      <c r="H18" s="16">
+        <f t="shared" ref="H18:AF18" si="4">H5*H13</f>
+        <v>14087746140.570616</v>
+      </c>
+      <c r="I18" s="16">
+        <f t="shared" si="4"/>
+        <v>14651255986.193439</v>
+      </c>
+      <c r="J18" s="16">
+        <f t="shared" si="4"/>
+        <v>15237306225.641176</v>
+      </c>
+      <c r="K18" s="16">
+        <f t="shared" si="4"/>
+        <v>15846798474.666822</v>
+      </c>
+      <c r="L18" s="16">
+        <f t="shared" si="4"/>
+        <v>16480670413.653496</v>
+      </c>
+      <c r="M18" s="16">
+        <f t="shared" si="4"/>
+        <v>17139897230.199636</v>
+      </c>
+      <c r="N18" s="16">
+        <f t="shared" si="4"/>
+        <v>17825493119.407623</v>
+      </c>
+      <c r="O18" s="16">
+        <f t="shared" si="4"/>
+        <v>18538512844.183929</v>
+      </c>
+      <c r="P18" s="16">
+        <f t="shared" si="4"/>
+        <v>19280053357.951286</v>
+      </c>
+      <c r="Q18" s="16">
+        <f t="shared" si="4"/>
+        <v>20051255492.269341</v>
+      </c>
+      <c r="R18" s="16">
+        <f t="shared" si="4"/>
+        <v>20051255492.269341</v>
+      </c>
+      <c r="S18" s="16">
+        <f t="shared" si="4"/>
+        <v>20051255492.269341</v>
+      </c>
+      <c r="T18" s="16">
+        <f t="shared" si="4"/>
+        <v>20051255492.269341</v>
+      </c>
+      <c r="U18" s="16">
+        <f t="shared" si="4"/>
+        <v>20051255492.269341</v>
+      </c>
+      <c r="V18" s="16">
+        <f t="shared" si="4"/>
+        <v>20051255492.269341</v>
+      </c>
+      <c r="W18" s="16">
+        <f t="shared" si="4"/>
+        <v>20051255492.269341</v>
+      </c>
+      <c r="X18" s="16">
+        <f t="shared" si="4"/>
+        <v>20051255492.269341</v>
+      </c>
+      <c r="Y18" s="16">
+        <f t="shared" si="4"/>
+        <v>20051255492.269341</v>
+      </c>
+      <c r="Z18" s="16">
+        <f t="shared" si="4"/>
+        <v>20051255492.269341</v>
+      </c>
+      <c r="AA18" s="16">
+        <f t="shared" si="4"/>
+        <v>20051255492.269341</v>
+      </c>
+      <c r="AB18" s="16">
+        <f t="shared" si="4"/>
+        <v>20051255492.269341</v>
+      </c>
+      <c r="AC18" s="16">
+        <f t="shared" si="4"/>
+        <v>20051255492.269341</v>
+      </c>
+      <c r="AD18" s="16">
+        <f t="shared" si="4"/>
+        <v>20051255492.269341</v>
+      </c>
+      <c r="AE18" s="16">
+        <f t="shared" si="4"/>
+        <v>20051255492.269341</v>
+      </c>
+      <c r="AF18" s="16">
+        <f t="shared" si="4"/>
+        <v>20051255492.269341</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" ht="12.75">
+      <c r="A19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="16">
+        <f>G6*G13</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="16">
+        <f t="shared" ref="H19:AF19" si="5">H6*H13</f>
+        <v>731466684</v>
+      </c>
+      <c r="I19" s="16">
+        <f t="shared" si="5"/>
+        <v>1521450702.72</v>
+      </c>
+      <c r="J19" s="16">
+        <f t="shared" si="5"/>
+        <v>1582308730.8288</v>
+      </c>
+      <c r="K19" s="16">
+        <f t="shared" si="5"/>
+        <v>1974721296.074342</v>
+      </c>
+      <c r="L19" s="16">
+        <f t="shared" si="5"/>
+        <v>2053710147.9173157</v>
+      </c>
+      <c r="M19" s="16">
+        <f t="shared" si="5"/>
+        <v>2135858553.8340085</v>
+      </c>
+      <c r="N19" s="16">
+        <f t="shared" si="5"/>
+        <v>1111571246.2693808</v>
+      </c>
+      <c r="O19" s="16">
+        <f t="shared" si="5"/>
+        <v>1156034096.120156</v>
+      </c>
+      <c r="P19" s="16">
+        <f t="shared" si="5"/>
+        <v>1202275459.964962</v>
+      </c>
+      <c r="Q19" s="16">
+        <f t="shared" si="5"/>
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="R19" s="16">
+        <f t="shared" si="5"/>
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="S19" s="16">
+        <f t="shared" si="5"/>
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="T19" s="16">
+        <f t="shared" si="5"/>
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="U19" s="16">
+        <f t="shared" si="5"/>
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="V19" s="16">
+        <f t="shared" si="5"/>
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="W19" s="16">
+        <f t="shared" si="5"/>
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="X19" s="16">
+        <f t="shared" si="5"/>
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="Y19" s="16">
+        <f t="shared" si="5"/>
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="Z19" s="16">
+        <f t="shared" si="5"/>
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="AA19" s="16">
+        <f t="shared" si="5"/>
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="AB19" s="16">
+        <f t="shared" si="5"/>
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="AC19" s="16">
+        <f t="shared" si="5"/>
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="AD19" s="16">
+        <f t="shared" si="5"/>
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="AE19" s="16">
+        <f t="shared" si="5"/>
+        <v>1250366478.3635607</v>
+      </c>
+      <c r="AF19" s="16">
+        <f t="shared" si="5"/>
+        <v>1250366478.3635607</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" ht="12.75">
+      <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="20">
-        <f t="shared" si="5"/>
+      <c r="C20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="16">
+        <f>G7*G14</f>
         <v>0</v>
       </c>
-      <c r="H17" s="20">
-        <f t="shared" si="5"/>
+      <c r="H20" s="16">
+        <f>H7*H14</f>
         <v>0</v>
       </c>
-      <c r="I17" s="20">
-        <f t="shared" si="5"/>
+      <c r="I20" s="16">
+        <f>I7*I14</f>
         <v>0</v>
       </c>
-      <c r="J17" s="20">
-        <f t="shared" si="5"/>
+      <c r="J20" s="16">
+        <f>J7*J14</f>
         <v>0</v>
       </c>
-      <c r="K17" s="20">
-        <f t="shared" si="5"/>
+      <c r="K20" s="16">
+        <f>K7*K14</f>
         <v>0</v>
       </c>
-      <c r="L17" s="20">
-        <f t="shared" si="5"/>
-        <v>2495899463.9590001</v>
-      </c>
-      <c r="M17" s="20">
-        <f t="shared" si="5"/>
-        <v>2495899463.9590001</v>
-      </c>
-      <c r="N17" s="20">
-        <f t="shared" si="5"/>
-        <v>3493819887.5889997</v>
-      </c>
-      <c r="O17" s="20">
-        <f t="shared" si="5"/>
-        <v>5849955000</v>
-      </c>
-      <c r="P17" s="20">
-        <f t="shared" si="5"/>
-        <v>5849955000</v>
-      </c>
-      <c r="Q17" s="20">
-        <f t="shared" si="5"/>
-        <v>8883265000</v>
-      </c>
-      <c r="R17" s="20">
-        <f t="shared" si="5"/>
-        <v>10833250000</v>
-      </c>
-      <c r="S17" s="20">
-        <f t="shared" si="5"/>
-        <v>12566570000</v>
-      </c>
-      <c r="T17" s="20">
-        <f t="shared" si="5"/>
-        <v>12566570000</v>
-      </c>
-      <c r="U17" s="20">
-        <f t="shared" si="5"/>
-        <v>12566570000</v>
-      </c>
-      <c r="V17" s="20">
-        <f t="shared" si="5"/>
-        <v>14083225000</v>
-      </c>
-      <c r="W17" s="20">
-        <f t="shared" si="5"/>
-        <v>14083225000</v>
-      </c>
-      <c r="X17" s="20">
-        <f t="shared" si="5"/>
-        <v>15773212000</v>
-      </c>
-      <c r="Y17" s="20">
-        <f t="shared" si="5"/>
-        <v>15773212000</v>
-      </c>
-      <c r="Z17" s="20">
-        <f t="shared" si="5"/>
-        <v>17333200000</v>
-      </c>
-      <c r="AA17" s="20">
-        <f t="shared" si="5"/>
-        <v>17333200000</v>
-      </c>
-      <c r="AB17" s="20">
-        <f t="shared" si="5"/>
-        <v>18676523000</v>
-      </c>
-      <c r="AC17" s="20">
-        <f t="shared" si="5"/>
-        <v>18676523000</v>
-      </c>
-      <c r="AD17" s="20">
-        <f t="shared" si="5"/>
-        <v>18676523000</v>
-      </c>
-      <c r="AE17" s="20">
-        <f t="shared" si="5"/>
-        <v>18676523000</v>
-      </c>
-      <c r="AF17" s="20">
-        <f t="shared" si="5"/>
-        <v>18676523000</v>
-      </c>
+      <c r="L20" s="16">
+        <f>L7*L14</f>
+        <v>4976477827.2000008</v>
+      </c>
+      <c r="M20" s="16">
+        <f>M7*M14</f>
+        <v>4792643625.9645901</v>
+      </c>
+      <c r="N20" s="16">
+        <f>N7*N14</f>
+        <v>6513336370.4258909</v>
+      </c>
+      <c r="O20" s="16">
+        <f>O7*O14</f>
+        <v>10652624550</v>
+      </c>
+      <c r="P20" s="16">
+        <f>P7*P14</f>
+        <v>10588499550</v>
+      </c>
+      <c r="Q20" s="16">
+        <f>Q7*Q14</f>
+        <v>15875542350</v>
+      </c>
+      <c r="R20" s="16">
+        <f>R7*R14</f>
+        <v>19097917500</v>
+      </c>
+      <c r="S20" s="16">
+        <f>S7*S14</f>
+        <v>20744665700</v>
+      </c>
+      <c r="T20" s="16">
+        <f>T7*T14</f>
+        <v>19848084300</v>
+      </c>
+      <c r="U20" s="16">
+        <f>U7*U14</f>
+        <v>18992584300</v>
+      </c>
+      <c r="V20" s="16">
+        <f>V7*V14</f>
+        <v>20372082250</v>
+      </c>
+      <c r="W20" s="16">
+        <f>W7*W14</f>
+        <v>19500000000</v>
+      </c>
+      <c r="X20" s="16">
+        <f>X7*X14</f>
+        <v>20908767880</v>
+      </c>
+      <c r="Y20" s="16">
+        <f>Y7*Y14</f>
+        <v>20020000000</v>
+      </c>
+      <c r="Z20" s="16">
+        <f>Z7*Z14</f>
+        <v>21066668000</v>
+      </c>
+      <c r="AA20" s="16">
+        <f>AA7*AA14</f>
+        <v>20176667999.999996</v>
+      </c>
+      <c r="AB20" s="16">
+        <f>AB7*AB14</f>
+        <v>20824484769.999996</v>
+      </c>
+      <c r="AC20" s="16">
+        <f>AC7*AC14</f>
+        <v>19944525000</v>
+      </c>
+      <c r="AD20" s="16">
+        <f>AD7*AD14</f>
+        <v>19104075000</v>
+      </c>
+      <c r="AE20" s="16">
+        <f>AE7*AE14</f>
+        <v>18299540230</v>
+      </c>
+      <c r="AF20" s="16">
+        <f>AF7*AF14</f>
+        <v>17530925000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" ht="15.75" customHeight="1">
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
+      <c r="R23" s="26"/>
+      <c r="S23" s="26"/>
+      <c r="T23" s="26"/>
+      <c r="U23" s="26"/>
+      <c r="V23" s="26"/>
+      <c r="W23" s="26"/>
+      <c r="X23" s="26"/>
+      <c r="Y23" s="26"/>
+      <c r="Z23" s="26"/>
+      <c r="AA23" s="26"/>
+      <c r="AB23" s="26"/>
+      <c r="AC23" s="26"/>
+      <c r="AD23" s="26"/>
+      <c r="AE23" s="26"/>
+      <c r="AF23" s="26"/>
+    </row>
+    <row r="24" spans="1:32" ht="15.75" customHeight="1">
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="25"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="25"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="25"/>
+      <c r="S24" s="25"/>
+      <c r="T24" s="25"/>
+      <c r="U24" s="25"/>
+      <c r="V24" s="25"/>
+      <c r="W24" s="25"/>
+      <c r="X24" s="25"/>
+      <c r="Y24" s="25"/>
+      <c r="Z24" s="25"/>
+      <c r="AA24" s="25"/>
+      <c r="AB24" s="25"/>
+      <c r="AC24" s="25"/>
+      <c r="AD24" s="25"/>
+      <c r="AE24" s="25"/>
+      <c r="AF24" s="25"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3989,7 +4213,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="8"/>
@@ -3999,7 +4223,7 @@
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="7"/>
@@ -4009,7 +4233,7 @@
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="7"/>
@@ -4026,729 +4250,729 @@
       <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A5" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="10"/>
+      <c r="A5" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="B5" s="22"/>
+      <c r="C5" s="11"/>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A6" s="29"/>
-      <c r="B6" s="30"/>
+      <c r="A6" s="23"/>
+      <c r="B6" s="24"/>
       <c r="C6" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="E6" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="F6" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="11" t="s">
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A7" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A7" s="12" t="s">
+      <c r="C7" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A8" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B8" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="F7" s="13" t="s">
+      <c r="C8" s="11" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A8" s="12" t="s">
+      <c r="D8" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B9" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C9" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A10" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A11" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A12" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A13" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A14" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A15" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A16" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A17" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A18" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A19" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A20" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A21" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A22" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A23" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A24" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A25" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A26" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A27" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="13.5">
+      <c r="A28" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="13.5">
+      <c r="A29" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="13.5">
+      <c r="A30" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="13.5">
+      <c r="A31" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="13.5">
+      <c r="A32" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="13.5">
+      <c r="A33" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="13.5">
+      <c r="A34" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="F34" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A9" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="13" t="s">
+    </row>
+    <row r="35" spans="1:6" ht="13.5">
+      <c r="A35" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="13.5">
+      <c r="A36" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="13.5">
+      <c r="A37" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="13.5">
+      <c r="A38" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F38" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A11" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A12" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A13" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A14" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A15" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A17" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A18" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A19" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A20" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A21" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" s="13" t="s">
+    </row>
+    <row r="39" spans="1:6" ht="13.5">
+      <c r="A39" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="D21" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="E21" s="13" t="s">
+      <c r="D39" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="E39" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="F21" s="13" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A22" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A23" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A24" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A25" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A26" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A27" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="13.5">
-      <c r="A28" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="13.5">
-      <c r="A29" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="13.5">
-      <c r="A30" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="13.5">
-      <c r="A31" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="13.5">
-      <c r="A32" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="13.5">
-      <c r="A33" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="13.5">
-      <c r="A34" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="13.5">
-      <c r="A35" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="13.5">
-      <c r="A36" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="F36" s="13" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="13.5">
-      <c r="A37" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="13.5">
-      <c r="A38" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="13.5">
-      <c r="A39" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="D39" s="13" t="s">
+      <c r="F39" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="E39" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="F39" s="13" t="s">
+    </row>
+    <row r="40" spans="1:6" ht="13.5">
+      <c r="A40" s="12" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" ht="16.5">
-      <c r="A40" s="14" t="s">
+      <c r="B40" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="C40" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="D40" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="D40" s="16" t="s">
+      <c r="E40" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="E40" s="16" t="s">
+      <c r="F40" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="F40" s="16" t="s">
+    </row>
+    <row r="41" spans="1:6" ht="13.5">
+      <c r="A41" s="14" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" ht="16.5">
-      <c r="A41" s="17" t="s">
+      <c r="B41" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="B41" s="18" t="s">
+      <c r="C41" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="C41" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="D41" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="E41" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="F41" s="19" t="s">
-        <v>216</v>
+      <c r="D41" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15">
@@ -12427,7 +12651,7 @@
   <mergeCells count="1">
     <mergeCell ref="A5:B6"/>
   </mergeCells>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12438,741 +12662,741 @@
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:6" ht="13.5">
-      <c r="A1" s="25" t="s">
-        <v>338</v>
+      <c r="A1" s="19" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="13.5">
-      <c r="A5" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="B5" s="28"/>
+      <c r="A5" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="B5" s="22"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
     </row>
-    <row r="6" spans="1:6" ht="16.5">
-      <c r="A6" s="29"/>
-      <c r="B6" s="30"/>
+    <row r="6" spans="1:6" ht="13.5">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24"/>
       <c r="C6" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="E6" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="F6" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="11" t="s">
+    </row>
+    <row r="7" spans="1:6" ht="13.5">
+      <c r="A7" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="16.5">
-      <c r="A7" s="12" t="s">
+      <c r="C7" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="13.5">
+      <c r="A8" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B8" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C8" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D8" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E8" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F8" s="11" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="16.5">
-      <c r="A8" s="12" t="s">
+    <row r="9" spans="1:6" ht="13.5">
+      <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B9" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C9" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D9" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E9" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F9" s="11" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="16.5">
-      <c r="A9" s="12" t="s">
+    <row r="10" spans="1:6" ht="13.5">
+      <c r="A10" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B10" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C10" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D10" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="E9" s="23" t="s">
+      <c r="E10" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F10" s="11" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="16.5">
-      <c r="A10" s="12" t="s">
+    <row r="11" spans="1:6" ht="13.5">
+      <c r="A11" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B11" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C11" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D11" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E11" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F11" s="11" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="16.5">
-      <c r="A11" s="12" t="s">
+    <row r="12" spans="1:6" ht="13.5">
+      <c r="A12" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B12" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C12" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="13.5">
+      <c r="A13" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D13" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="E11" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="F11" s="23" t="s">
+      <c r="E13" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="16.5">
-      <c r="A12" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="D12" s="24" t="s">
+    <row r="14" spans="1:6" ht="13.5">
+      <c r="A14" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="13.5">
+      <c r="A15" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="13.5">
+      <c r="A16" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="13.5">
+      <c r="A17" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="13.5">
+      <c r="A18" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="13.5">
+      <c r="A19" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="13.5">
+      <c r="A20" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="13.5">
+      <c r="A21" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="13.5">
+      <c r="A22" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="13.5">
+      <c r="A23" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="13.5">
+      <c r="A24" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="13.5">
+      <c r="A25" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="13.5">
+      <c r="A26" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="13.5">
+      <c r="A27" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="13.5">
+      <c r="A28" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="13.5">
+      <c r="A29" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="13.5">
+      <c r="A30" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="13.5">
+      <c r="A31" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="13.5">
+      <c r="A32" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="13.5">
+      <c r="A33" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="13.5">
+      <c r="A34" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="13.5">
+      <c r="A35" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="13.5">
+      <c r="A36" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="13.5">
+      <c r="A37" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="13.5">
+      <c r="A38" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="13.5">
+      <c r="A39" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="13.5">
+      <c r="A40" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="E12" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="16.5">
-      <c r="A13" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>254</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>285</v>
-      </c>
-      <c r="F13" s="23" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="16.5">
-      <c r="A14" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="16.5">
-      <c r="A15" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>255</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="F15" s="23" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="16.5">
-      <c r="A16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>227</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>288</v>
-      </c>
-      <c r="F16" s="24" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="16.5">
-      <c r="A17" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>257</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>262</v>
-      </c>
-      <c r="F17" s="23" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="16.5">
-      <c r="A18" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>229</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="F18" s="24" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="16.5">
-      <c r="A19" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="E19" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="F19" s="23" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="16.5">
-      <c r="A20" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="F20" s="24" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="16.5">
-      <c r="A21" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>260</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="F21" s="23" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="16.5">
-      <c r="A22" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>232</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>261</v>
-      </c>
-      <c r="E22" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="16.5">
-      <c r="A23" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>262</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="F23" s="23" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="16.5">
-      <c r="A24" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>263</v>
-      </c>
-      <c r="E24" s="24" t="s">
-        <v>294</v>
-      </c>
-      <c r="F24" s="24" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="16.5">
-      <c r="A25" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>176</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>264</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="F25" s="23" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="16.5">
-      <c r="A26" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>235</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="E26" s="24" t="s">
-        <v>296</v>
-      </c>
-      <c r="F26" s="24" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="16.5">
-      <c r="A27" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="D27" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>297</v>
-      </c>
-      <c r="F27" s="23" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="16.5">
-      <c r="A28" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="D28" s="24" t="s">
-        <v>267</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>298</v>
-      </c>
-      <c r="F28" s="24" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="16.5">
-      <c r="A29" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="D29" s="23" t="s">
-        <v>268</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>299</v>
-      </c>
-      <c r="F29" s="23" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="16.5">
-      <c r="A30" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="D30" s="24" t="s">
-        <v>269</v>
-      </c>
-      <c r="E30" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="F30" s="24" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="16.5">
-      <c r="A31" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>301</v>
-      </c>
-      <c r="F31" s="23" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="16.5">
-      <c r="A32" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="D32" s="24" t="s">
-        <v>271</v>
-      </c>
-      <c r="E32" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="F32" s="24" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="16.5">
-      <c r="A33" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>242</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>272</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>303</v>
-      </c>
-      <c r="F33" s="23" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="16.5">
-      <c r="A34" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="D34" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="E34" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="F34" s="24" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="16.5">
-      <c r="A35" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="D35" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="E35" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="F35" s="23" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="16.5">
-      <c r="A36" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="D36" s="24" t="s">
-        <v>274</v>
-      </c>
-      <c r="E36" s="24" t="s">
-        <v>304</v>
-      </c>
-      <c r="F36" s="24" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="16.5">
-      <c r="A37" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="D37" s="23" t="s">
-        <v>275</v>
-      </c>
-      <c r="E37" s="23" t="s">
-        <v>305</v>
-      </c>
-      <c r="F37" s="23" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="16.5">
-      <c r="A38" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C38" s="24" t="s">
-        <v>245</v>
-      </c>
-      <c r="D38" s="24" t="s">
+      <c r="B40" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="D40" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="E38" s="24" t="s">
+      <c r="E40" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="F38" s="24" t="s">
+      <c r="F40" s="11" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="16.5">
-      <c r="A39" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C39" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="D39" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="E39" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="F39" s="23" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="16.5">
-      <c r="A40" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="C40" s="24" t="s">
+    <row r="41" spans="1:6" ht="13.5">
+      <c r="A41" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="C41" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="D40" s="24" t="s">
+      <c r="D41" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="E40" s="24" t="s">
+      <c r="E41" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="F40" s="24" t="s">
+      <c r="F41" s="11" t="s">
         <v>336</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="16.5">
-      <c r="A41" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="B41" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="C41" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="D41" s="23" t="s">
-        <v>278</v>
-      </c>
-      <c r="E41" s="23" t="s">
-        <v>308</v>
-      </c>
-      <c r="F41" s="23" t="s">
-        <v>337</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A5:B6"/>
   </mergeCells>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13183,741 +13407,741 @@
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:6" ht="13.5">
-      <c r="A1" s="26" t="s">
-        <v>339</v>
+      <c r="A1" s="20" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="13.5">
-      <c r="A5" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="B5" s="28"/>
+      <c r="A5" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="B5" s="22"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
     </row>
-    <row r="6" spans="1:6" ht="16.5">
-      <c r="A6" s="29"/>
-      <c r="B6" s="30"/>
+    <row r="6" spans="1:6" ht="13.5">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24"/>
       <c r="C6" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="E6" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="F6" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="11" t="s">
+    </row>
+    <row r="7" spans="1:6" ht="13.5">
+      <c r="A7" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="16.5">
-      <c r="A7" s="12" t="s">
+      <c r="C7" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="13.5">
+      <c r="A8" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B8" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C8" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="13.5">
+      <c r="A9" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="13.5">
+      <c r="A10" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="D7" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="E7" s="23" t="s">
+      <c r="E10" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="13.5">
+      <c r="A11" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="13.5">
+      <c r="A12" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="13.5">
+      <c r="A13" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="13.5">
+      <c r="A14" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="13.5">
+      <c r="A15" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="13.5">
+      <c r="A16" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="13.5">
+      <c r="A17" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="13.5">
+      <c r="A18" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="13.5">
+      <c r="A19" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="13.5">
+      <c r="A20" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="F7" s="23" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="16.5">
-      <c r="A8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="24" t="s">
+      <c r="E20" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="13.5">
+      <c r="A21" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="13.5">
+      <c r="A22" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="13.5">
+      <c r="A23" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="13.5">
+      <c r="A24" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="13.5">
+      <c r="A25" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="13.5">
+      <c r="A26" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="13.5">
+      <c r="A27" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="13.5">
+      <c r="A28" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="13.5">
+      <c r="A29" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="13.5">
+      <c r="A30" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="13.5">
+      <c r="A31" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="13.5">
+      <c r="A32" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="13.5">
+      <c r="A33" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="13.5">
+      <c r="A34" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="D34" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>346</v>
-      </c>
-      <c r="E8" s="24" t="s">
+      <c r="E34" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="13.5">
+      <c r="A35" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="13.5">
+      <c r="A36" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="13.5">
+      <c r="A37" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="13.5">
+      <c r="A38" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="13.5">
+      <c r="A39" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="13.5">
+      <c r="A40" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="C40" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="F8" s="24" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="16.5">
-      <c r="A9" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="16.5">
-      <c r="A10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>199</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="16.5">
-      <c r="A11" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>356</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="F11" s="23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="16.5">
-      <c r="A12" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>357</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>371</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="16.5">
-      <c r="A13" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>340</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>372</v>
-      </c>
-      <c r="F13" s="23" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="16.5">
-      <c r="A14" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="16.5">
-      <c r="A15" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>341</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>358</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="F15" s="23" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="16.5">
-      <c r="A16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>342</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>359</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="F16" s="24" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="16.5">
-      <c r="A17" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>343</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>360</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>373</v>
-      </c>
-      <c r="F17" s="23" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="16.5">
-      <c r="A18" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>344</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>361</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>374</v>
-      </c>
-      <c r="F18" s="24" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="16.5">
-      <c r="A19" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>345</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="E19" s="23" t="s">
-        <v>375</v>
-      </c>
-      <c r="F19" s="23" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="16.5">
-      <c r="A20" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>351</v>
-      </c>
-      <c r="F20" s="24" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="16.5">
-      <c r="A21" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>346</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>346</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>376</v>
-      </c>
-      <c r="F21" s="23" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="16.5">
-      <c r="A22" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>347</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>362</v>
-      </c>
-      <c r="E22" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="16.5">
-      <c r="A23" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>348</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>365</v>
-      </c>
-      <c r="F23" s="23" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="16.5">
-      <c r="A24" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>349</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="E24" s="24" t="s">
-        <v>377</v>
-      </c>
-      <c r="F24" s="24" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="16.5">
-      <c r="A25" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="F25" s="23" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="16.5">
-      <c r="A26" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>350</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>363</v>
-      </c>
-      <c r="E26" s="24" t="s">
-        <v>378</v>
-      </c>
-      <c r="F26" s="24" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="16.5">
-      <c r="A27" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="D27" s="23" t="s">
-        <v>364</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>379</v>
-      </c>
-      <c r="F27" s="23" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="16.5">
-      <c r="A28" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="D28" s="24" t="s">
-        <v>365</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>380</v>
-      </c>
-      <c r="F28" s="24" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="16.5">
-      <c r="A29" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>345</v>
-      </c>
-      <c r="D29" s="23" t="s">
-        <v>366</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>352</v>
-      </c>
-      <c r="F29" s="23" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="16.5">
-      <c r="A30" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>351</v>
-      </c>
-      <c r="D30" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="E30" s="24" t="s">
-        <v>381</v>
-      </c>
-      <c r="F30" s="24" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="16.5">
-      <c r="A31" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>345</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="F31" s="23" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="16.5">
-      <c r="A32" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="D32" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="E32" s="24" t="s">
-        <v>382</v>
-      </c>
-      <c r="F32" s="24" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="16.5">
-      <c r="A33" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>352</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>360</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>383</v>
-      </c>
-      <c r="F33" s="23" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="16.5">
-      <c r="A34" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="D34" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="E34" s="24" t="s">
-        <v>196</v>
-      </c>
-      <c r="F34" s="24" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="16.5">
-      <c r="A35" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>353</v>
-      </c>
-      <c r="D35" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="E35" s="23" t="s">
-        <v>376</v>
-      </c>
-      <c r="F35" s="23" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="16.5">
-      <c r="A36" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="D36" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="E36" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="F36" s="24" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="16.5">
-      <c r="A37" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="D37" s="23" t="s">
+      <c r="D40" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="E37" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="F37" s="23" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="16.5">
-      <c r="A38" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C38" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="D38" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="E38" s="24" t="s">
+      <c r="E40" s="11" t="s">
         <v>384</v>
       </c>
-      <c r="F38" s="24" t="s">
+      <c r="F40" s="11" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="16.5">
-      <c r="A39" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C39" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="D39" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="E39" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="F39" s="23" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="16.5">
-      <c r="A40" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="C40" s="24" t="s">
+    <row r="41" spans="1:6" ht="13.5">
+      <c r="A41" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="C41" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="D40" s="24" t="s">
+      <c r="D41" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="E40" s="24" t="s">
+      <c r="E41" s="11" t="s">
         <v>385</v>
       </c>
-      <c r="F40" s="24" t="s">
+      <c r="F41" s="11" t="s">
         <v>398</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="16.5">
-      <c r="A41" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="B41" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="C41" s="23" t="s">
-        <v>355</v>
-      </c>
-      <c r="D41" s="23" t="s">
-        <v>370</v>
-      </c>
-      <c r="E41" s="23" t="s">
-        <v>386</v>
-      </c>
-      <c r="F41" s="23" t="s">
-        <v>399</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A5:B6"/>
   </mergeCells>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13928,736 +14152,736 @@
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="5" spans="1:6" ht="13.5">
-      <c r="A5" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="B5" s="28"/>
+      <c r="A5" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="B5" s="22"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
     </row>
-    <row r="6" spans="1:6" ht="16.5">
-      <c r="A6" s="29"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="11" t="s">
+    <row r="6" spans="1:6" ht="13.5">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="E6" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="F6" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="11" t="s">
+    </row>
+    <row r="7" spans="1:6" ht="13.5">
+      <c r="A7" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="16.5">
-      <c r="A7" s="12" t="s">
+      <c r="C7" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="13.5">
+      <c r="A8" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B8" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="23" t="s">
-        <v>392</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>346</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>392</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="16.5">
-      <c r="A8" s="12" t="s">
+      <c r="C8" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="13.5">
+      <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B9" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="24" t="s">
-        <v>376</v>
-      </c>
-      <c r="D8" s="24" t="s">
+      <c r="C9" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="13.5">
+      <c r="A10" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="13.5">
+      <c r="A11" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="13.5">
+      <c r="A12" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="13.5">
+      <c r="A13" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="13.5">
+      <c r="A14" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="13.5">
+      <c r="A15" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="13.5">
+      <c r="A16" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="13.5">
+      <c r="A17" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="13.5">
+      <c r="A18" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="13.5">
+      <c r="A19" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="E8" s="24" t="s">
-        <v>400</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="16.5">
-      <c r="A9" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="23" t="s">
+      <c r="E19" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="F19" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="13.5">
+      <c r="A20" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="13.5">
+      <c r="A21" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="13.5">
+      <c r="A22" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="13.5">
+      <c r="A23" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="13.5">
+      <c r="A24" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="13.5">
+      <c r="A25" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="E9" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="16.5">
-      <c r="A10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>376</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>353</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="F10" s="24" t="s">
+      <c r="D25" s="6" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="16.5">
-      <c r="A11" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>368</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="F11" s="23" t="s">
+      <c r="E25" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="13.5">
+      <c r="A26" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="13.5">
+      <c r="A27" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="13.5">
+      <c r="A28" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="13.5">
+      <c r="A29" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="13.5">
+      <c r="A30" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="13.5">
+      <c r="A31" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="13.5">
+      <c r="A32" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="13.5">
+      <c r="A33" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="13.5">
+      <c r="A34" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="13.5">
+      <c r="A35" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="13.5">
+      <c r="A36" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F36" s="6" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="16.5">
-      <c r="A12" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>400</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>409</v>
-      </c>
-      <c r="E12" s="24" t="s">
+    <row r="37" spans="1:6" ht="13.5">
+      <c r="A37" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="13.5">
+      <c r="A38" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="13.5">
+      <c r="A39" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="13.5">
+      <c r="A40" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="F12" s="24" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="16.5">
-      <c r="A13" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>401</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="F13" s="23" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="16.5">
-      <c r="A14" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>353</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="16.5">
-      <c r="A15" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>402</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>418</v>
-      </c>
-      <c r="F15" s="23" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="16.5">
-      <c r="A16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>403</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>405</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="F16" s="24" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="16.5">
-      <c r="A17" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="F17" s="23" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="16.5">
-      <c r="A18" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>96</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>349</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="F18" s="24" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="16.5">
-      <c r="A19" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>404</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>410</v>
-      </c>
-      <c r="E19" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="F19" s="23" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="16.5">
-      <c r="A20" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>376</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>353</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="F20" s="24" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="16.5">
-      <c r="A21" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>400</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>400</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>400</v>
-      </c>
-      <c r="F21" s="23" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="16.5">
-      <c r="A22" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>411</v>
-      </c>
-      <c r="E22" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="16.5">
-      <c r="A23" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>412</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="F23" s="23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="16.5">
-      <c r="A24" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>368</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>368</v>
-      </c>
-      <c r="E24" s="24" t="s">
-        <v>202</v>
-      </c>
-      <c r="F24" s="24" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="16.5">
-      <c r="A25" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="F25" s="23" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="16.5">
-      <c r="A26" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>405</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="E26" s="24" t="s">
-        <v>419</v>
-      </c>
-      <c r="F26" s="24" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="16.5">
-      <c r="A27" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>260</v>
-      </c>
-      <c r="D27" s="23" t="s">
-        <v>413</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>420</v>
-      </c>
-      <c r="F27" s="23" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="16.5">
-      <c r="A28" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>397</v>
-      </c>
-      <c r="D28" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>421</v>
-      </c>
-      <c r="F28" s="24" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="16.5">
-      <c r="A29" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="D29" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>404</v>
-      </c>
-      <c r="F29" s="23" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="16.5">
-      <c r="A30" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="D30" s="24" t="s">
-        <v>414</v>
-      </c>
-      <c r="E30" s="24" t="s">
-        <v>402</v>
-      </c>
-      <c r="F30" s="24" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="16.5">
-      <c r="A31" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="F31" s="23" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="16.5">
-      <c r="A32" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" s="24" t="s">
+      <c r="B40" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="D32" s="24" t="s">
+      <c r="D40" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="E32" s="24" t="s">
-        <v>422</v>
-      </c>
-      <c r="F32" s="24" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="16.5">
-      <c r="A33" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>352</v>
-      </c>
-      <c r="F33" s="23" t="s">
+      <c r="E40" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="F40" s="6" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="16.5">
-      <c r="A34" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>376</v>
-      </c>
-      <c r="D34" s="24" t="s">
-        <v>376</v>
-      </c>
-      <c r="E34" s="24" t="s">
-        <v>346</v>
-      </c>
-      <c r="F34" s="24" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="16.5">
-      <c r="A35" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>376</v>
-      </c>
-      <c r="D35" s="23" t="s">
-        <v>353</v>
-      </c>
-      <c r="E35" s="23" t="s">
-        <v>346</v>
-      </c>
-      <c r="F35" s="23" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="16.5">
-      <c r="A36" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="D36" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="E36" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="F36" s="24" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="16.5">
-      <c r="A37" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>353</v>
-      </c>
-      <c r="D37" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="E37" s="23" t="s">
-        <v>353</v>
-      </c>
-      <c r="F37" s="23" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="16.5">
-      <c r="A38" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C38" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="D38" s="24" t="s">
-        <v>368</v>
-      </c>
-      <c r="E38" s="24" t="s">
-        <v>423</v>
-      </c>
-      <c r="F38" s="24" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="16.5">
-      <c r="A39" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C39" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="D39" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="E39" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="F39" s="23" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="16.5">
-      <c r="A40" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="C40" s="24" t="s">
+    <row r="41" spans="1:6" ht="13.5">
+      <c r="A41" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="D40" s="24" t="s">
+      <c r="D41" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="E40" s="24" t="s">
+      <c r="E41" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="F40" s="24" t="s">
+      <c r="F41" s="6" t="s">
         <v>430</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="16.5">
-      <c r="A41" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="B41" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="C41" s="23" t="s">
-        <v>408</v>
-      </c>
-      <c r="D41" s="23" t="s">
-        <v>417</v>
-      </c>
-      <c r="E41" s="23" t="s">
-        <v>425</v>
-      </c>
-      <c r="F41" s="23" t="s">
-        <v>431</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A5:B6"/>
   </mergeCells>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>